--- a/database/event/6136/event_6136_evp_summary.xlsx
+++ b/database/event/6136/event_6136_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.5151</v>
+        <v>9.482900000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5842</v>
+        <v>5.5653</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4225</v>
+        <v>3.3341</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5151</v>
+        <v>9.482900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3515</v>
+        <v>4.3194</v>
       </c>
       <c r="G2" t="n">
         <v>5.1636</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5201</v>
+        <v>4.4697</v>
       </c>
       <c r="I2" t="n">
         <v>4.5835</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9389</v>
       </c>
       <c r="C3" t="n">
-        <v>4.6993</v>
+        <v>4.6592</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8134</v>
+        <v>2.7189</v>
       </c>
       <c r="E3" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9389</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6945</v>
+        <v>3.6261</v>
       </c>
       <c r="G3" t="n">
         <v>4.3128</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6945</v>
+        <v>3.6261</v>
       </c>
       <c r="I3" t="n">
         <v>3.7813</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3659</v>
+        <v>6.294</v>
       </c>
       <c r="C4" t="n">
-        <v>3.736</v>
+        <v>3.6938</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1503</v>
+        <v>2.0636</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3659</v>
+        <v>6.294</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3513</v>
+        <v>5.2794</v>
       </c>
       <c r="G4" t="n">
         <v>1.0146</v>
       </c>
       <c r="H4" t="n">
-        <v>6.0878</v>
+        <v>5.9751</v>
       </c>
       <c r="I4" t="n">
         <v>6.2308</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3413</v>
+        <v>6.2757</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7216</v>
+        <v>3.6831</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1404</v>
+        <v>2.0563</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3413</v>
+        <v>6.2757</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5423</v>
+        <v>3.4767</v>
       </c>
       <c r="G5" t="n">
         <v>2.799</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5423</v>
+        <v>3.4767</v>
       </c>
       <c r="I5" t="n">
         <v>3.6255</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.987</v>
+        <v>5.9856</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5136</v>
+        <v>3.5128</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9973</v>
+        <v>1.9408</v>
       </c>
       <c r="E6" t="n">
-        <v>5.987</v>
+        <v>5.9856</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3838</v>
+        <v>0.3824</v>
       </c>
       <c r="G6" t="n">
         <v>5.6032</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3838</v>
+        <v>0.3824</v>
       </c>
       <c r="I6" t="n">
         <v>0.3856</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7484</v>
+        <v>5.713</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3736</v>
+        <v>3.3528</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9009</v>
+        <v>1.8321</v>
       </c>
       <c r="E7" t="n">
-        <v>5.7484</v>
+        <v>5.713</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1747</v>
+        <v>3.1393</v>
       </c>
       <c r="G7" t="n">
         <v>2.5737</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1747</v>
+        <v>3.1393</v>
       </c>
       <c r="I7" t="n">
         <v>3.2192</v>
@@ -778,7 +778,7 @@
         <v>3.3323</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8724</v>
+        <v>1.8182</v>
       </c>
       <c r="E8" t="n">
         <v>5.678</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3525</v>
+        <v>5.2826</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1413</v>
+        <v>3.1002</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7409</v>
+        <v>1.6607</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3525</v>
+        <v>5.2826</v>
       </c>
       <c r="F9" t="n">
-        <v>5.2441</v>
+        <v>5.1742</v>
       </c>
       <c r="G9" t="n">
         <v>0.1084</v>
       </c>
       <c r="H9" t="n">
-        <v>5.9196</v>
+        <v>5.81</v>
       </c>
       <c r="I9" t="n">
         <v>6.0587</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.1512</v>
+        <v>5.0967</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0231</v>
+        <v>2.9911</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6596</v>
+        <v>1.5866</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1512</v>
+        <v>5.0967</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4118</v>
+        <v>4.3573</v>
       </c>
       <c r="G10" t="n">
         <v>0.7393999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6147</v>
+        <v>4.5292</v>
       </c>
       <c r="I10" t="n">
         <v>4.7231</v>
@@ -916,7 +916,7 @@
         <v>2.3127</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1706</v>
+        <v>1.1261</v>
       </c>
       <c r="E11" t="n">
         <v>3.9407</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6714</v>
+        <v>3.6571</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1547</v>
+        <v>2.1463</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0618</v>
+        <v>1.0131</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6714</v>
+        <v>3.6571</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6714</v>
+        <v>0.8685</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.7886</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6714</v>
+        <v>0.8685</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7229</v>
+        <v>0.8685</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.7886</v>
       </c>
       <c r="K12" t="n">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7229</v>
+        <v>3.6571</v>
       </c>
       <c r="N12" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6571</v>
+        <v>3.6304</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1463</v>
+        <v>2.1306</v>
       </c>
       <c r="D13" t="n">
-        <v>1.056</v>
+        <v>1.0024</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6571</v>
+        <v>3.6304</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8685</v>
+        <v>3.6304</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7886</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8685</v>
+        <v>3.6304</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8685</v>
+        <v>3.7229</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7886</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>74</v>
+        <v>296</v>
       </c>
       <c r="L13" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6571</v>
+        <v>3.7229</v>
       </c>
       <c r="N13" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14">
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.3939</v>
+        <v>3.3561</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9918</v>
+        <v>1.9696</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9497</v>
+        <v>0.8932</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3939</v>
+        <v>3.3561</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3939</v>
+        <v>3.3561</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3939</v>
+        <v>3.3561</v>
       </c>
       <c r="I14" t="n">
         <v>3.4416</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.3123</v>
+        <v>3.2936</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9439</v>
+        <v>1.9329</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9167</v>
+        <v>0.8683</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3123</v>
+        <v>3.2936</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5132</v>
+        <v>2.4945</v>
       </c>
       <c r="G15" t="n">
         <v>0.7991</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5132</v>
+        <v>2.4945</v>
       </c>
       <c r="I15" t="n">
         <v>2.5366</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9097</v>
+        <v>2.8988</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7076</v>
+        <v>1.7012</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7541</v>
+        <v>0.711</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9097</v>
+        <v>2.8988</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9097</v>
+        <v>2.8988</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9097</v>
+        <v>2.8988</v>
       </c>
       <c r="I16" t="n">
         <v>2.9232</v>
@@ -1192,7 +1192,7 @@
         <v>1.658</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7199</v>
+        <v>0.6816</v>
       </c>
       <c r="E17" t="n">
         <v>2.8251</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3045</v>
+        <v>2.2788</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3525</v>
+        <v>1.3374</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.464</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3045</v>
+        <v>2.2788</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3045</v>
+        <v>2.2788</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3045</v>
+        <v>2.2788</v>
       </c>
       <c r="I18" t="n">
         <v>2.3368</v>
@@ -1284,7 +1284,7 @@
         <v>1.2475</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4374</v>
+        <v>0.403</v>
       </c>
       <c r="E19" t="n">
         <v>2.1257</v>
@@ -1330,7 +1330,7 @@
         <v>1.2335</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4277</v>
+        <v>0.3934</v>
       </c>
       <c r="E20" t="n">
         <v>2.1018</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0466</v>
+        <v>2.0238</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2011</v>
+        <v>1.1877</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4054</v>
+        <v>0.3624</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0466</v>
+        <v>2.0238</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0466</v>
+        <v>2.0238</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0466</v>
+        <v>2.0238</v>
       </c>
       <c r="I21" t="n">
         <v>2.0753</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9397</v>
+        <v>1.9243</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1384</v>
+        <v>1.1293</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3622</v>
+        <v>0.3227</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9397</v>
+        <v>1.9243</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0675</v>
+        <v>2.0521</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1278</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0675</v>
+        <v>2.0521</v>
       </c>
       <c r="I22" t="n">
         <v>2.0868</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9148</v>
+        <v>1.8935</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1238</v>
+        <v>1.1113</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3522</v>
+        <v>0.3105</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9148</v>
+        <v>1.8935</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9148</v>
+        <v>1.8935</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9148</v>
+        <v>1.8935</v>
       </c>
       <c r="I23" t="n">
         <v>1.9417</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5309</v>
+        <v>1.5252</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8984</v>
+        <v>0.8951</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1971</v>
+        <v>0.1637</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5309</v>
+        <v>1.5252</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5309</v>
+        <v>1.5252</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5309</v>
+        <v>1.5252</v>
       </c>
       <c r="I24" t="n">
         <v>1.538</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4095</v>
+        <v>1.3991</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8272</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.148</v>
+        <v>0.1135</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4095</v>
+        <v>1.3991</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4095</v>
+        <v>1.3991</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4095</v>
+        <v>1.3991</v>
       </c>
       <c r="I25" t="n">
         <v>1.4227</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2734</v>
+        <v>1.265</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7473</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0931</v>
+        <v>0.0601</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2734</v>
+        <v>1.265</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0881</v>
+        <v>1.265</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.8147</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0881</v>
+        <v>1.265</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1076</v>
+        <v>1.265</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8147</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="L26" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2929</v>
+        <v>1.265</v>
       </c>
       <c r="N26" t="n">
-        <v>243</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.265</v>
+        <v>1.2579</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7382</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0897</v>
+        <v>0.0572</v>
       </c>
       <c r="E27" t="n">
-        <v>1.265</v>
+        <v>1.2579</v>
       </c>
       <c r="F27" t="n">
-        <v>1.265</v>
+        <v>2.0726</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.8147</v>
       </c>
       <c r="H27" t="n">
-        <v>1.265</v>
+        <v>2.0726</v>
       </c>
       <c r="I27" t="n">
-        <v>1.265</v>
+        <v>2.1076</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.8147</v>
       </c>
       <c r="K27" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M27" t="n">
-        <v>1.265</v>
+        <v>1.2929</v>
       </c>
       <c r="N27" t="n">
-        <v>166</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>0.7312</v>
       </c>
       <c r="D28" t="n">
-        <v>0.082</v>
+        <v>0.0525</v>
       </c>
       <c r="E28" t="n">
         <v>1.2459</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.224</v>
+        <v>1.219</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7183</v>
+        <v>0.7154</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0731</v>
+        <v>0.0417</v>
       </c>
       <c r="E29" t="n">
-        <v>1.224</v>
+        <v>1.219</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5598</v>
+        <v>1.8833</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3358</v>
+        <v>-0.6643</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5598</v>
+        <v>1.8833</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5744</v>
+        <v>1.5265</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3358</v>
+        <v>-0.6643</v>
       </c>
       <c r="K29" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="L29" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2386</v>
+        <v>0.8622</v>
       </c>
       <c r="N29" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.219</v>
+        <v>1.2124</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7154</v>
+        <v>0.7115</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0711</v>
+        <v>0.0391</v>
       </c>
       <c r="E30" t="n">
-        <v>1.219</v>
+        <v>1.2124</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8833</v>
+        <v>1.5482</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6643</v>
+        <v>-0.3358</v>
       </c>
       <c r="H30" t="n">
-        <v>1.8833</v>
+        <v>1.5482</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5265</v>
+        <v>1.5744</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6643</v>
+        <v>-0.3358</v>
       </c>
       <c r="K30" t="n">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="L30" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8622</v>
+        <v>1.2386</v>
       </c>
       <c r="N30" t="n">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31">
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1538</v>
+        <v>1.1452</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6771</v>
+        <v>0.6721</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0447</v>
+        <v>0.0123</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1538</v>
+        <v>1.1452</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1538</v>
+        <v>1.1452</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1538</v>
+        <v>1.1452</v>
       </c>
       <c r="I31" t="n">
         <v>1.1646</v>
@@ -1882,7 +1882,7 @@
         <v>0.6167</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0031</v>
+        <v>-0.0253</v>
       </c>
       <c r="E32" t="n">
         <v>1.0508</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.0148</v>
+        <v>1.011</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5956</v>
+        <v>0.5933</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0114</v>
+        <v>-0.0411</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0148</v>
+        <v>1.011</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0148</v>
+        <v>1.011</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0148</v>
+        <v>1.011</v>
       </c>
       <c r="I33" t="n">
         <v>1.0195</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9</v>
+        <v>0.8625</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5282</v>
+        <v>0.5062</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0578</v>
+        <v>-0.1003</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9</v>
+        <v>0.8625</v>
       </c>
       <c r="F34" t="n">
-        <v>2.03</v>
+        <v>1.9925</v>
       </c>
       <c r="G34" t="n">
         <v>-1.13</v>
       </c>
       <c r="H34" t="n">
-        <v>2.03</v>
+        <v>1.9925</v>
       </c>
       <c r="I34" t="n">
         <v>2.0777</v>
@@ -2020,7 +2020,7 @@
         <v>0.5056</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0733</v>
+        <v>-0.1007</v>
       </c>
       <c r="E35" t="n">
         <v>0.8615</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8577</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5034</v>
+        <v>0.4996</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.1048</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8577</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8577</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8577</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="I36" t="n">
         <v>0.8657</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5863</v>
+        <v>0.5841</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3441</v>
+        <v>0.3428</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1845</v>
+        <v>-0.2112</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5863</v>
+        <v>0.5841</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5863</v>
+        <v>0.5841</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5863</v>
+        <v>0.5841</v>
       </c>
       <c r="I37" t="n">
         <v>0.589</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4958</v>
+        <v>0.487</v>
       </c>
       <c r="C38" t="n">
-        <v>0.291</v>
+        <v>0.2858</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2211</v>
+        <v>-0.2499</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4958</v>
+        <v>0.487</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3765</v>
+        <v>0.487</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8807</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3765</v>
+        <v>0.487</v>
       </c>
       <c r="I38" t="n">
-        <v>1.4088</v>
+        <v>0.487</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8807</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="L38" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5281</v>
+        <v>0.487</v>
       </c>
       <c r="N38" t="n">
-        <v>312</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.487</v>
+        <v>0.4703</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2858</v>
+        <v>0.276</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2246</v>
+        <v>-0.2565</v>
       </c>
       <c r="E39" t="n">
-        <v>0.487</v>
+        <v>0.4703</v>
       </c>
       <c r="F39" t="n">
-        <v>0.487</v>
+        <v>1.351</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.8807</v>
       </c>
       <c r="H39" t="n">
-        <v>0.487</v>
+        <v>1.351</v>
       </c>
       <c r="I39" t="n">
-        <v>0.487</v>
+        <v>1.4088</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.8807</v>
       </c>
       <c r="K39" t="n">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M39" t="n">
-        <v>0.487</v>
+        <v>0.5281</v>
       </c>
       <c r="N39" t="n">
-        <v>222</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4055</v>
+        <v>0.4025</v>
       </c>
       <c r="C40" t="n">
-        <v>0.238</v>
+        <v>0.2362</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2575</v>
+        <v>-0.2836</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4055</v>
+        <v>0.4025</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4055</v>
+        <v>0.4025</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4055</v>
+        <v>0.4025</v>
       </c>
       <c r="I40" t="n">
         <v>0.4093</v>
@@ -2296,7 +2296,7 @@
         <v>0.2034</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2813</v>
+        <v>-0.3058</v>
       </c>
       <c r="E41" t="n">
         <v>0.3466</v>
@@ -2342,7 +2342,7 @@
         <v>0.1983</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2849</v>
+        <v>-0.3093</v>
       </c>
       <c r="E42" t="n">
         <v>0.3379</v>
@@ -2388,7 +2388,7 @@
         <v>0.1873</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2924</v>
+        <v>-0.3167</v>
       </c>
       <c r="E43" t="n">
         <v>0.3192</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2496</v>
+        <v>0.2487</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1465</v>
+        <v>0.146</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3205</v>
+        <v>-0.3448</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2496</v>
+        <v>0.2487</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2496</v>
+        <v>0.2487</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2496</v>
+        <v>0.2487</v>
       </c>
       <c r="I44" t="n">
         <v>0.2508</v>
@@ -2480,7 +2480,7 @@
         <v>0.1203</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3385</v>
+        <v>-0.3622</v>
       </c>
       <c r="E45" t="n">
         <v>0.205</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1905</v>
+        <v>0.1898</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1118</v>
+        <v>0.1114</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3444</v>
+        <v>-0.3683</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1905</v>
+        <v>0.1898</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1905</v>
+        <v>0.1898</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1905</v>
+        <v>0.1898</v>
       </c>
       <c r="I46" t="n">
         <v>0.1914</v>
@@ -2572,7 +2572,7 @@
         <v>0.0858</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3623</v>
+        <v>-0.3857</v>
       </c>
       <c r="E47" t="n">
         <v>0.1462</v>
@@ -2618,7 +2618,7 @@
         <v>0.0653</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3764</v>
+        <v>-0.3996</v>
       </c>
       <c r="E48" t="n">
         <v>0.1112</v>
@@ -2664,7 +2664,7 @@
         <v>0.0379</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3953</v>
+        <v>-0.4182</v>
       </c>
       <c r="E49" t="n">
         <v>0.0645</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.094</v>
+        <v>-0.1107</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0552</v>
+        <v>-0.065</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4593</v>
+        <v>-0.488</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.094</v>
+        <v>-0.1107</v>
       </c>
       <c r="F50" t="n">
-        <v>0.903</v>
+        <v>0.8863</v>
       </c>
       <c r="G50" t="n">
         <v>-0.997</v>
       </c>
       <c r="H50" t="n">
-        <v>0.903</v>
+        <v>0.8863</v>
       </c>
       <c r="I50" t="n">
         <v>0.9242</v>
@@ -2756,7 +2756,7 @@
         <v>-0.08690000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4812</v>
+        <v>-0.5029</v>
       </c>
       <c r="E51" t="n">
         <v>-0.148</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2031</v>
+        <v>-0.1866</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1192</v>
+        <v>-0.1095</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5034</v>
+        <v>-0.5183</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2031</v>
+        <v>-0.1866</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.4756</v>
+        <v>-1.4591</v>
       </c>
       <c r="G52" t="n">
         <v>1.2725</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.4756</v>
+        <v>-1.4591</v>
       </c>
       <c r="I52" t="n">
         <v>-1.4963</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2869</v>
+        <v>-0.2837</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1684</v>
+        <v>-0.1665</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5373</v>
+        <v>-0.5569</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2869</v>
+        <v>-0.2837</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2869</v>
+        <v>-0.2837</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2869</v>
+        <v>-0.2837</v>
       </c>
       <c r="I53" t="n">
         <v>-0.2909</v>
@@ -2894,7 +2894,7 @@
         <v>-0.2213</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5737</v>
+        <v>-0.5941</v>
       </c>
       <c r="E54" t="n">
         <v>-0.3771</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4002</v>
+        <v>-0.3972</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2349</v>
+        <v>-0.2331</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.583</v>
+        <v>-0.6022</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4002</v>
+        <v>-0.3972</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4002</v>
+        <v>-0.3972</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4002</v>
+        <v>-0.3972</v>
       </c>
       <c r="I55" t="n">
         <v>-0.4039</v>
@@ -2986,7 +2986,7 @@
         <v>-0.3183</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6405</v>
+        <v>-0.66</v>
       </c>
       <c r="E56" t="n">
         <v>-0.5424</v>
@@ -3032,7 +3032,7 @@
         <v>-0.341</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6561</v>
+        <v>-0.6754</v>
       </c>
       <c r="E57" t="n">
         <v>-0.581</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.7582</v>
+        <v>-0.7553</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.445</v>
+        <v>-0.4433</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7277</v>
+        <v>-0.7448</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.7582</v>
+        <v>-0.7553</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.7582</v>
+        <v>-0.7553</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.7582</v>
+        <v>-0.7553</v>
       </c>
       <c r="I58" t="n">
         <v>-0.7617</v>
@@ -3124,7 +3124,7 @@
         <v>-0.4501</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7312</v>
+        <v>-0.7494</v>
       </c>
       <c r="E59" t="n">
         <v>-0.7669</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.782</v>
+        <v>-0.779</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.4589</v>
+        <v>-0.4572</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7373</v>
+        <v>-0.7543</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.782</v>
+        <v>-0.779</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.782</v>
+        <v>-0.779</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.782</v>
+        <v>-0.779</v>
       </c>
       <c r="I60" t="n">
         <v>-0.7856</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.8693</v>
+        <v>-0.87</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.5102</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7725</v>
+        <v>-0.7905</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.8693</v>
+        <v>-0.87</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0887</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G61" t="n">
         <v>-0.958</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0887</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I61" t="n">
         <v>0.0895</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.888</v>
+        <v>-0.8781</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.5211</v>
+        <v>-0.5153</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7801</v>
+        <v>-0.7937</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.888</v>
+        <v>-0.8781</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.888</v>
+        <v>-0.8781</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.888</v>
+        <v>-0.8781</v>
       </c>
       <c r="I62" t="n">
         <v>-0.9005</v>
@@ -3308,7 +3308,7 @@
         <v>-0.5311</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.787</v>
+        <v>-0.8045</v>
       </c>
       <c r="E63" t="n">
         <v>-0.905</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.9615</v>
+        <v>-0.9508</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.5643</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8098</v>
+        <v>-0.8227</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.9615</v>
+        <v>-0.9508</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.9615</v>
+        <v>-0.9508</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.9615</v>
+        <v>-0.9508</v>
       </c>
       <c r="I64" t="n">
         <v>-0.975</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5828</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8225</v>
+        <v>-0.8395</v>
       </c>
       <c r="E65" t="n">
         <v>-0.993</v>
@@ -3446,7 +3446,7 @@
         <v>-0.6086</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8403</v>
+        <v>-0.8571</v>
       </c>
       <c r="E66" t="n">
         <v>-1.037</v>
@@ -3492,7 +3492,7 @@
         <v>-0.6216</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.8659</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0592</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1279</v>
+        <v>-1.1153</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6619</v>
+        <v>-0.6545</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.877</v>
+        <v>-0.8882</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.1279</v>
+        <v>-1.1153</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.1279</v>
+        <v>-1.1153</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.1279</v>
+        <v>-1.1153</v>
       </c>
       <c r="I68" t="n">
         <v>-1.1437</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6687</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8817</v>
+        <v>-0.8979</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1395</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6888</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8955</v>
+        <v>-0.9115</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1736</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7008</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9038</v>
+        <v>-0.9197</v>
       </c>
       <c r="E71" t="n">
         <v>-1.1942</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8399</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-1.0141</v>
       </c>
       <c r="E72" t="n">
         <v>-1.4312</v>
@@ -3768,7 +3768,7 @@
         <v>-0.8401999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9997</v>
+        <v>-1.0143</v>
       </c>
       <c r="E73" t="n">
         <v>-1.4317</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8908</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0346</v>
+        <v>-1.0486</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5179</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.6315</v>
+        <v>-1.6133</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.9575</v>
+        <v>-0.9468</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0805</v>
+        <v>-1.0866</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.6315</v>
+        <v>-1.6133</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.6315</v>
+        <v>-1.6133</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.6315</v>
+        <v>-1.6133</v>
       </c>
       <c r="I75" t="n">
         <v>-1.6544</v>
@@ -3906,7 +3906,7 @@
         <v>-1.1131</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1876</v>
+        <v>-1.1996</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8967</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1738</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E77" t="n">
         <v>-2</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.2464</v>
+        <v>-2.2381</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.3184</v>
+        <v>-1.3135</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3289</v>
+        <v>-1.3356</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.2464</v>
+        <v>-2.2381</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.2464</v>
+        <v>-2.2381</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.2464</v>
+        <v>-2.2381</v>
       </c>
       <c r="I78" t="n">
         <v>-2.2569</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.328</v>
+        <v>-2.3034</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.3662</v>
+        <v>-1.3518</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3618</v>
+        <v>-1.3616</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.328</v>
+        <v>-2.3034</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.328</v>
+        <v>-1.3034</v>
       </c>
       <c r="G79" t="n">
         <v>-1</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.328</v>
+        <v>-1.3034</v>
       </c>
       <c r="I79" t="n">
         <v>-1.3592</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.3598</v>
+        <v>-2.351</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.3849</v>
+        <v>-1.3797</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3747</v>
+        <v>-1.3805</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.3598</v>
+        <v>-2.351</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.3598</v>
+        <v>-2.351</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.3598</v>
+        <v>-2.351</v>
       </c>
       <c r="I80" t="n">
         <v>-2.3708</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.0725</v>
+        <v>-4.0298</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.3901</v>
+        <v>-2.365</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0666</v>
+        <v>-2.0494</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.0725</v>
+        <v>-4.0298</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.3062</v>
+        <v>-2.2635</v>
       </c>
       <c r="G81" t="n">
         <v>-1.7663</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.3062</v>
+        <v>-2.2635</v>
       </c>
       <c r="I81" t="n">
         <v>-2.3604</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-4.1017</v>
+        <v>-4.0559</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.4072</v>
+        <v>-2.3803</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.0784</v>
+        <v>-2.0598</v>
       </c>
       <c r="E82" t="n">
-        <v>-4.1017</v>
+        <v>-4.0559</v>
       </c>
       <c r="F82" t="n">
-        <v>-4.1017</v>
+        <v>-4.0559</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-4.1017</v>
+        <v>-4.0559</v>
       </c>
       <c r="I82" t="n">
         <v>-4.1592</v>
